--- a/database.xlsx
+++ b/database.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="MASTER" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="CORPOGESTAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="QUIMETALES PELIGROSOS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,6 +682,156 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DFG567</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DFG567</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>240</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DFG567</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Sin foto</t>
         </is>
@@ -905,4 +1056,220 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>url_memo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>url_camion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DFG567</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DFG567</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>240</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DFG567</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,6 +832,406 @@
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>300</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>150</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>170</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PET limpio</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>170</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PET limpio</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>40</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PET limpio</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Sin foto</t>
         </is>
@@ -848,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1448,406 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>200</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>170</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PET limpio</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>170</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PET limpio</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yeison</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FGB567</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PET limpio</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Sin foto</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -11,6 +11,7 @@
     <sheet name="MASTER" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="CORPOGESTAR" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="QUIMETALES PELIGROSOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RECICLA ORIENTE" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1233,306 @@
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>28</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Sin foto</t>
         </is>
@@ -2072,4 +2373,370 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>url_memo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>url_camion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fernando</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SDF456</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>28</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -12,6 +12,7 @@
     <sheet name="CORPOGESTAR" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="QUIMETALES PELIGROSOS" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="RECICLA ORIENTE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="QUIMETALES NO PELIGROSOS" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1533,6 +1534,456 @@
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>80</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>23</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>110</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>120</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>130</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>140</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Sin foto</t>
         </is>
@@ -2739,4 +3190,520 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>url_memo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>url_camion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>80</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>110</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>130</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>duvan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>JUH678</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>140</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,6 +1984,256 @@
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>235</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tela sucia</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>120</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tela sucia</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>130</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Sin foto</t>
         </is>
@@ -2616,7 +2866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2816,6 +3066,256 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>60</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>235</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tela sucia</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BVF567</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tela sucia</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>130</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin observaciones</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sin foto</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Sin foto</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2266,6 +2266,156 @@
       <c r="J37" t="inlineStr">
         <is>
           <t>Sin foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fabián</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GHV567</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>80</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>No hubo observaciones</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/MEMO_20260420_194849.jpg</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/CAMION_20260420_194849.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Fabián</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>GHV567</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>40</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>No hubo observaciones</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/MEMO_20260420_194849.jpg</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/CAMION_20260420_194849.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Fabián</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GHV567</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>120</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>No hubo observaciones</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/MEMO_20260420_194849.jpg</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/CAMION_20260420_194849.jpg</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2985,6 +3135,156 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fabián</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GHV567</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>80</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No hubo observaciones</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/MEMO_20260420_194849.jpg</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/CAMION_20260420_194849.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fabián</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GHV567</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>40</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>No hubo observaciones</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/MEMO_20260420_194849.jpg</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/CAMION_20260420_194849.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fabián</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GHV567</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>No hubo observaciones</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/MEMO_20260420_194849.jpg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/CAMION_20260420_194849.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2418,6 +2418,132 @@
           <t>https://raw.githubusercontent.com/alejandraho013/registro-salida-residuos/main/fotos/CAMION_20260420_194849.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DFG456</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>50</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DFG456</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>70</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DFG456</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2430,7 +2556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3285,6 +3411,132 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DFG456</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>50</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DFG456</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>70</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DFG456</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="MASTER" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CORPOGESTAR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="QUIMETALES PELIGROSOS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2544,6 +2545,132 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>HGG679</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tela sucia</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>600</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>HGG679</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Residuos laboratorio</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>200</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>HGG679</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>300</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3540,4 +3667,180 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HGG679</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tela sucia</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HGG679</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Residuos laboratorio</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HGG679</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -1,67 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.biblioteca 902\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D161F2DA-0BC7-4CBE-9B81-EB9140699EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MASTER" sheetId="1" r:id="rId1"/>
+    <sheet name="MASTER" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="QUIMETALES PELIGROSOS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>mes</t>
-  </si>
-  <si>
-    <t>empresa</t>
-  </si>
-  <si>
-    <t>conductor</t>
-  </si>
-  <si>
-    <t>placa</t>
-  </si>
-  <si>
-    <t>tipo_residuo</t>
-  </si>
-  <si>
-    <t>peso_kg</t>
-  </si>
-  <si>
-    <t>novedades</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -80,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -382,34 +409,2270 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>25</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>25</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="MASTER" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="QUIMETALES PELIGROSOS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="QUIMETALES NO PELIGROSOS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,6 +1535,366 @@
         <v>14.7</v>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>48</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>51</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2678,4 +3039,420 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>48</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>51</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -1,67 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.biblioteca 902\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D161F2DA-0BC7-4CBE-9B81-EB9140699EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MASTER" sheetId="1" r:id="rId1"/>
+    <sheet name="MASTER" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="QUIMETALES NO PELIGROSOS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>mes</t>
-  </si>
-  <si>
-    <t>empresa</t>
-  </si>
-  <si>
-    <t>conductor</t>
-  </si>
-  <si>
-    <t>placa</t>
-  </si>
-  <si>
-    <t>tipo_residuo</t>
-  </si>
-  <si>
-    <t>peso_kg</t>
-  </si>
-  <si>
-    <t>novedades</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -80,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -382,34 +409,830 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>51</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>51</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="MASTER" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="QUIMETALES NO PELIGROSOS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="QUIMETALES PELIGROSOS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +815,1086 @@
         <v>65.8</v>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>27</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>25</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1238,4 +2319,1140 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>25</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,6 +1895,166 @@
         <v>14.7</v>
       </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1911,7 +2071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,6 +2471,166 @@
         <v>65.8</v>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2055,6 +2055,46 @@
         <v>97.5</v>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2647,7 +2687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3772,6 +3812,46 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscar Javier </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,6 +2095,46 @@
         <v>508.4</v>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erys Martinez </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>2257.15</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2111,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2671,6 +2711,46 @@
         <v>97.5</v>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erys Martinez </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2257.15</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2135,6 +2135,166 @@
         <v>2257.15</v>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1164.99</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iluminarias </t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2767,7 +2927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3932,6 +4092,166 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1164.99</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iluminarias </t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>RAEE</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2295,6 +2295,46 @@
         <v>106.5</v>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2311,7 +2351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2911,6 +2951,46 @@
         <v>2257.15</v>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2335,6 +2335,46 @@
         <v>94.2</v>
       </c>
       <c r="H48" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3007,7 +3047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4332,6 +4372,46 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2375,46 @@
         <v>444.5</v>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3047,7 +3087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4412,6 +4452,46 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2415,6 +2415,46 @@
         <v>136.1</v>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>2657.4</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2431,7 +2471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3071,6 +3111,46 @@
         <v>94.2</v>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2657.4</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2455,6 +2455,46 @@
         <v>2657.4</v>
       </c>
       <c r="H51" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3167,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4572,6 +4612,46 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2495,6 +2495,46 @@
         <v>367.9</v>
       </c>
       <c r="H52" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3207,7 +3247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4652,6 +4692,46 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2535,6 +2535,46 @@
         <v>355.2</v>
       </c>
       <c r="H53" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3247,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4732,6 +4772,46 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2575,6 +2575,46 @@
         <v>221.6</v>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>665.1</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2591,7 +2631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3271,6 +3311,46 @@
         <v>2657.4</v>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>665.1</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2615,6 +2615,46 @@
         <v>665.1</v>
       </c>
       <c r="H55" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>157</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3367,7 +3407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4892,6 +4932,46 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>157</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,6 +2655,46 @@
         <v>157</v>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2671,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3391,6 +3431,46 @@
         <v>665.1</v>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quimetales NO Peligrosos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2695,6 +2695,46 @@
         <v>45.5</v>
       </c>
       <c r="H57" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>752.3</v>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3487,7 +3527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5052,6 +5092,46 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Quimetales Peligrosos</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>752.3</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,67 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.biblioteca 902\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E8FC58-78AE-442A-B91A-30EF4650F666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MASTER" sheetId="1" r:id="rId1"/>
+    <sheet name="MASTER" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VEOLIA APROVECHABLES" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>mes</t>
-  </si>
-  <si>
-    <t>empresa</t>
-  </si>
-  <si>
-    <t>conductor</t>
-  </si>
-  <si>
-    <t>placa</t>
-  </si>
-  <si>
-    <t>tipo_residuo</t>
-  </si>
-  <si>
-    <t>peso_kg</t>
-  </si>
-  <si>
-    <t>novedades</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -80,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -382,34 +409,190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,67 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.biblioteca 902\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E8FC58-78AE-442A-B91A-30EF4650F666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MASTER" sheetId="1" r:id="rId1"/>
+    <sheet name="MASTER" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VEOLIA APROVECHABLES" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>mes</t>
-  </si>
-  <si>
-    <t>empresa</t>
-  </si>
-  <si>
-    <t>conductor</t>
-  </si>
-  <si>
-    <t>placa</t>
-  </si>
-  <si>
-    <t>tipo_residuo</t>
-  </si>
-  <si>
-    <t>peso_kg</t>
-  </si>
-  <si>
-    <t>novedades</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -80,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -382,34 +409,190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="MASTER" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="VEOLIA APROVECHABLES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="VEOLIA PELIGROSOS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +495,86 @@
         <v>645.4</v>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EQX598</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EQX598</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>276.9</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -598,4 +679,140 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EQX598</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EQX598</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>276.9</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,46 @@
         <v>276.9</v>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jose David </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>EQX598</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -687,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +852,46 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jose David </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EQX598</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,46 @@
         <v>132.9</v>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2182.75</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -631,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +751,46 @@
         <v>645.4</v>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2182.75</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -10,6 +10,7 @@
     <sheet name="MASTER" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="VEOLIA APROVECHABLES" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="VEOLIA PELIGROSOS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CICLO TOTAL" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,6 +656,206 @@
         <v>2182.75</v>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cartón contaminado</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>648.75</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tubo Plega</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>285.3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Papel de archivo</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PET sucio</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -975,4 +1176,260 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cartón contaminado</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>648.75</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tubo Plega</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>285.3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Papel de archivo</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CICLO TOTAL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PET sucio</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,6 +856,46 @@
         <v>22.85</v>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jersson</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>STS153</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -872,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,6 +1032,46 @@
         <v>2182.75</v>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jersson</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>STS153</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,6 +896,46 @@
         <v>102.3</v>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>424.4</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -912,7 +952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1072,6 +1112,46 @@
         <v>102.3</v>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>424.4</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,6 +936,46 @@
         <v>424.4</v>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>539.9</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1168,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1328,6 +1368,46 @@
         <v>132.9</v>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>539.9</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -11,6 +11,7 @@
     <sheet name="VEOLIA APROVECHABLES" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="VEOLIA PELIGROSOS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CICLO TOTAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CORPOGESTAR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +977,126 @@
         <v>539.9</v>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lenys Aubrey</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>987.6900000000001</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lenys Aubrey</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>331.95</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lenys Aubrey</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>241.65</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1672,4 +1793,180 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lenys Aubrey</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>987.6900000000001</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lenys Aubrey</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>331.95</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lenys Aubrey</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>241.65</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,6 +1097,46 @@
         <v>241.65</v>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1329,7 +1369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1529,6 +1569,46 @@
         <v>539.9</v>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,6 +1137,86 @@
         <v>425.1</v>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>469</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1153,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1353,6 +1433,86 @@
         <v>424.4</v>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>469</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1217,46 @@
         <v>469</v>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>236.7</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1529,7 +1569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1769,6 +1809,46 @@
         <v>425.1</v>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>236.7</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,6 +1257,46 @@
         <v>236.7</v>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>985.2</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1273,7 +1313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,6 +1593,46 @@
         <v>469</v>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>985.2</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,6 +1297,46 @@
         <v>985.2</v>
       </c>
       <c r="H22" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1649,7 +1689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1929,6 +1969,46 @@
         <v>236.7</v>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1337,6 +1337,46 @@
         <v>372.8</v>
       </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1689,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2009,6 +2049,46 @@
         <v>372.8</v>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,6 +1377,46 @@
         <v>487.5</v>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FUY530</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>544.4</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1729,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2129,46 @@
         <v>487.5</v>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FUY530</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>544.4</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -12,6 +12,7 @@
     <sheet name="VEOLIA PELIGROSOS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CICLO TOTAL" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="CORPOGESTAR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RECICLA ORIENTE" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,6 +1418,126 @@
         <v>544.4</v>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Edwin Sanchez</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>798.25</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Edwin Sanchez</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>309.55</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Edwin Sanchez</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Papel de archivo</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2609,4 +2730,180 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conductor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tipo_residuo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Edwin Sanchez</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>798.25</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Edwin Sanchez</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>309.55</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Edwin Sanchez</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EQX498</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Papel de archivo</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1538,6 +1538,46 @@
         <v>12.15</v>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>215</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1890,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2290,6 +2330,46 @@
         <v>544.4</v>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>January_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>215</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1578,6 +1578,46 @@
         <v>215</v>
       </c>
       <c r="H29" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1620.27</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1594,7 +1634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1914,6 +1954,46 @@
         <v>985.2</v>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1620.27</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,6 +1618,46 @@
         <v>1620.27</v>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2010,7 +2050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2450,6 +2490,46 @@
         <v>215</v>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,6 +1658,206 @@
         <v>328.9</v>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>628.1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>392.8</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PET sucio</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2802,7 +3002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2962,6 +3162,206 @@
         <v>241.65</v>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>628.1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>392.8</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Lenys Arbey</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PET sucio</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,6 +1858,46 @@
         <v>15.6</v>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2250,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2730,6 +2770,46 @@
         <v>328.9</v>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,6 +1898,86 @@
         <v>182.7</v>
       </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>297.1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -1914,7 +1994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2274,6 +2354,86 @@
         <v>1620.27</v>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>297.1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1978,6 +1978,46 @@
         <v>99.8</v>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2450,7 +2490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2970,6 +3010,46 @@
         <v>182.7</v>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2018,6 +2018,46 @@
         <v>214.6</v>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>266.3</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2034,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2474,6 +2514,46 @@
         <v>99.8</v>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>266.3</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2058,6 +2058,126 @@
         <v>266.3</v>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Yorman Salas</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SNP296</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Cartón contaminado</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>638.45</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Yorman Salas</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SNP296</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Yorman Salas</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SNP296</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>256.15</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3402,7 +3522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3762,6 +3882,126 @@
         <v>15.6</v>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yorman Salas</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SNP296</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cartón contaminado</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>638.45</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Yorman Salas</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SNP296</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Yorman Salas</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SNP296</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>256.15</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2178,6 +2178,86 @@
         <v>256.15</v>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Torner</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2690,7 +2770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3250,6 +3330,86 @@
         <v>214.6</v>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Torner</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2258,6 +2258,46 @@
         <v>6.8</v>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>594.5</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2274,7 +2314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2754,6 +2794,46 @@
         <v>266.3</v>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>594.5</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2298,6 +2298,46 @@
         <v>594.5</v>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>209.9</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2850,7 +2890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3490,6 +3530,46 @@
         <v>6.8</v>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>209.9</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2338,6 +2338,46 @@
         <v>209.9</v>
       </c>
       <c r="H48" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>650.05</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2354,7 +2394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2874,6 +2914,46 @@
         <v>594.5</v>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>650.05</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2378,6 +2378,46 @@
         <v>650.05</v>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>291.3</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2394,7 +2434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2954,6 +2994,46 @@
         <v>650.05</v>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>291.3</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2418,6 +2418,46 @@
         <v>291.3</v>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>254</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3050,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3730,6 +3770,46 @@
         <v>209.9</v>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>254</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2458,6 +2458,166 @@
         <v>254</v>
       </c>
       <c r="H51" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Lenis Aubey</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>296.1</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Lenis Aubey</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>298.45</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lenis Aubey</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Lenis Aubey</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4082,7 +4242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4562,6 +4722,166 @@
         <v>256.15</v>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lenis Aubey</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>296.1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lenis Aubey</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>298.45</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lenis Aubey</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lenis Aubey</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BRA710</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2618,6 +2618,46 @@
         <v>94.09999999999999</v>
       </c>
       <c r="H55" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3250,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3970,6 +4010,46 @@
         <v>254</v>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2658,6 +2658,46 @@
         <v>295.4</v>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1023</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2674,7 +2714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3274,6 +3314,46 @@
         <v>291.3</v>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1023</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,6 +2698,46 @@
         <v>1023</v>
       </c>
       <c r="H57" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>661.5</v>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2714,7 +2754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3354,6 +3394,46 @@
         <v>1023</v>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>661.5</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2738,6 +2738,126 @@
         <v>661.5</v>
       </c>
       <c r="H58" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Chatarra Electrónica</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3450,7 +3570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4210,6 +4330,126 @@
         <v>295.4</v>
       </c>
       <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Chatarra Electrónica</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2858,6 +2858,86 @@
         <v>0.4</v>
       </c>
       <c r="H61" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>751.5</v>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -2874,7 +2954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3554,6 +3634,86 @@
         <v>661.5</v>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>751.5</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2938,6 +2938,46 @@
         <v>751.5</v>
       </c>
       <c r="H63" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3730,7 +3770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4610,6 +4650,46 @@
         <v>0.4</v>
       </c>
       <c r="H22" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>February_2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FUV530</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2978,6 +2978,46 @@
         <v>139.7</v>
       </c>
       <c r="H64" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3770,7 +3810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4690,6 +4730,46 @@
         <v>139.7</v>
       </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3018,6 +3018,46 @@
         <v>342.9</v>
       </c>
       <c r="H65" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="H66" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3034,7 +3074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3794,6 +3834,46 @@
         <v>751.5</v>
       </c>
       <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3058,6 +3058,46 @@
         <v>676.4</v>
       </c>
       <c r="H66" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>WHV707</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>407</v>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3890,7 +3930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4850,6 +4890,46 @@
         <v>342.9</v>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WHV707</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>407</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3098,6 +3098,46 @@
         <v>407</v>
       </c>
       <c r="H67" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1608.2</v>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3114,7 +3154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3914,6 +3954,46 @@
         <v>676.4</v>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1608.2</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3138,6 +3138,46 @@
         <v>1608.2</v>
       </c>
       <c r="H68" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>302</v>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4010,7 +4050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5010,6 +5050,46 @@
         <v>407</v>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>302</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3178,6 +3178,86 @@
         <v>302</v>
       </c>
       <c r="H69" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>FUQ530</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>372</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>FUQ530</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H71" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4050,7 +4130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5090,6 +5170,86 @@
         <v>302</v>
       </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FUQ530</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>372</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FUQ530</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3258,6 +3258,86 @@
         <v>0.8</v>
       </c>
       <c r="H71" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jaime Pabón</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jaime Pabón</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3274,7 +3354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4114,6 +4194,86 @@
         <v>1608.2</v>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jaime Pabón</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jaime Pabón</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3338,6 +3338,86 @@
         <v>300.9</v>
       </c>
       <c r="H73" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4290,7 +4370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5410,6 +5490,86 @@
         <v>0.8</v>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3418,6 +3418,86 @@
         <v>1.3</v>
       </c>
       <c r="H75" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>845.8</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3434,7 +3514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4354,6 +4434,86 @@
         <v>300.9</v>
       </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>845.8</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3498,6 +3498,46 @@
         <v>37.1</v>
       </c>
       <c r="H77" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>FUY530</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4530,7 +4570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5730,6 +5770,46 @@
         <v>1.3</v>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FUY530</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3538,6 +3538,46 @@
         <v>182.2</v>
       </c>
       <c r="H78" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EQK668</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3554,7 +3594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4554,6 +4594,46 @@
         <v>37.1</v>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>EQK668</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3578,6 +3578,206 @@
         <v>205.6</v>
       </c>
       <c r="H79" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>736.6</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lamparas fluorescentes</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Chatarra Electrónica</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>403</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Torner</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>38</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Residuos laboratorio</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>14</v>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4650,7 +4850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5890,6 +6090,206 @@
         <v>182.2</v>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>736.6</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lamparas fluorescentes</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Chatarra Electrónica</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>403</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Torner</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>38</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WHY707</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Residuos laboratorio</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>14</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3778,6 +3778,46 @@
         <v>14</v>
       </c>
       <c r="H84" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>277.7</v>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4850,7 +4890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6290,6 +6330,46 @@
         <v>14</v>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>277.7</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3818,6 +3818,86 @@
         <v>277.7</v>
       </c>
       <c r="H85" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3834,7 +3914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4874,6 +4954,86 @@
         <v>205.6</v>
       </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EQX668</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3898,6 +3898,86 @@
         <v>335.3</v>
       </c>
       <c r="H87" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>FUY530</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FUY530</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>693</v>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -3914,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5034,6 +5114,86 @@
         <v>335.3</v>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FUY530</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FUY530</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>693</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3978,6 +3978,46 @@
         <v>693</v>
       </c>
       <c r="H89" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -5210,7 +5250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6690,6 +6730,46 @@
         <v>277.7</v>
       </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4018,6 +4018,46 @@
         <v>375.8</v>
       </c>
       <c r="H90" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1027.5</v>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4034,7 +4074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5234,6 +5274,46 @@
         <v>693</v>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1027.5</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4058,6 +4058,46 @@
         <v>1027.5</v>
       </c>
       <c r="H91" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -5330,7 +5370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6850,6 +6890,46 @@
         <v>375.8</v>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>March_2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4098,6 +4098,46 @@
         <v>385.1</v>
       </c>
       <c r="H92" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="H93" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4114,7 +4154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5354,6 +5394,46 @@
         <v>1027.5</v>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4138,6 +4138,46 @@
         <v>94.2</v>
       </c>
       <c r="H93" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -5450,7 +5490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7010,6 +7050,46 @@
         <v>385.1</v>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4178,6 +4178,166 @@
         <v>444.5</v>
       </c>
       <c r="H94" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Sólidos contaminados</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1164.99</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Aceites</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Chatarra electrónica</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Iluminaria</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="H98" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4194,7 +4354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5474,6 +5634,166 @@
         <v>94.2</v>
       </c>
       <c r="H32" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sólidos contaminados</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1164.99</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Aceites</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Chatarra electrónica</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Iluminaria</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4338,6 +4338,46 @@
         <v>29.15</v>
       </c>
       <c r="H98" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>2257.15</v>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4354,7 +4394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,6 +5834,46 @@
         <v>29.15</v>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>2257.15</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4378,6 +4378,46 @@
         <v>2257.15</v>
       </c>
       <c r="H99" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="H100" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4394,7 +4434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5874,6 +5914,46 @@
         <v>2257.15</v>
       </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4418,6 +4418,46 @@
         <v>292.5</v>
       </c>
       <c r="H100" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -5970,7 +6010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7570,6 +7610,46 @@
         <v>444.5</v>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4458,6 +4458,46 @@
         <v>508.4</v>
       </c>
       <c r="H101" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>516</v>
+      </c>
+      <c r="H102" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4474,7 +4514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5994,6 +6034,46 @@
         <v>292.5</v>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>516</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4498,6 +4498,46 @@
         <v>516</v>
       </c>
       <c r="H102" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="H103" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6090,7 +6130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7730,6 +7770,46 @@
         <v>508.4</v>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4538,6 +4538,46 @@
         <v>136.1</v>
       </c>
       <c r="H103" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>2657.4</v>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4554,7 +4594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6114,6 +6154,46 @@
         <v>516</v>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Erys Martinez</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GDW871</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>2657.4</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4578,6 +4578,46 @@
         <v>2657.4</v>
       </c>
       <c r="H104" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6210,7 +6250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7890,6 +7930,46 @@
         <v>136.1</v>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4618,6 +4618,86 @@
         <v>367.4</v>
       </c>
       <c r="H105" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Torner</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6250,7 +6330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7970,6 +8050,86 @@
         <v>367.4</v>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Torner</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4698,6 +4698,46 @@
         <v>0.1</v>
       </c>
       <c r="H107" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="H108" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6330,7 +6370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8130,6 +8170,46 @@
         <v>0.1</v>
       </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4738,6 +4738,46 @@
         <v>221.6</v>
       </c>
       <c r="H108" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>665.1</v>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4754,7 +4794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6354,6 +6394,46 @@
         <v>2657.4</v>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>665.1</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4778,6 +4778,46 @@
         <v>665.1</v>
       </c>
       <c r="H109" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>157</v>
+      </c>
+      <c r="H110" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6450,7 +6490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8290,6 +8330,46 @@
         <v>221.6</v>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>April_2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>157</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4818,6 +4818,46 @@
         <v>157</v>
       </c>
       <c r="H110" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H111" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4834,7 +4874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6474,6 +6514,46 @@
         <v>665.1</v>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4858,6 +4858,46 @@
         <v>45.5</v>
       </c>
       <c r="H111" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Hernan Alonzo</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>752.3</v>
+      </c>
+      <c r="H112" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6570,7 +6610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8450,6 +8490,46 @@
         <v>157</v>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Hernan Alonzo</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>752.3</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4898,6 +4898,86 @@
         <v>752.3</v>
       </c>
       <c r="H112" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>534</v>
+      </c>
+      <c r="H114" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -4914,7 +4994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6594,6 +6674,86 @@
         <v>45.5</v>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>534</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4978,6 +4978,46 @@
         <v>534</v>
       </c>
       <c r="H114" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>748.1</v>
+      </c>
+      <c r="H115" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6770,7 +6810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8690,6 +8730,46 @@
         <v>752.3</v>
       </c>
       <c r="H48" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>748.1</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5018,6 +5018,46 @@
         <v>748.1</v>
       </c>
       <c r="H115" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>280</v>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6810,7 +6850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8770,6 +8810,46 @@
         <v>748.1</v>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>280</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5058,46 @@
         <v>280</v>
       </c>
       <c r="H116" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>222.3</v>
+      </c>
+      <c r="H117" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -5074,7 +5114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6834,6 +6874,46 @@
         <v>534</v>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>222.3</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5098,6 +5098,126 @@
         <v>222.3</v>
       </c>
       <c r="H117" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Reactivos de laboratorio</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6930,7 +7050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8930,6 +9050,126 @@
         <v>280</v>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Reactivos de laboratorio</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5218,6 +5218,46 @@
         <v>36.6</v>
       </c>
       <c r="H120" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>SVO395</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1003</v>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7050,7 +7090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9170,6 +9210,46 @@
         <v>36.6</v>
       </c>
       <c r="H53" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SVO395</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1003</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5258,6 +5258,46 @@
         <v>1003</v>
       </c>
       <c r="H121" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>39</v>
+      </c>
+      <c r="H122" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -5274,7 +5314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7074,6 +7114,46 @@
         <v>222.3</v>
       </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>39</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5298,6 +5298,46 @@
         <v>39</v>
       </c>
       <c r="H122" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>428.7</v>
+      </c>
+      <c r="H123" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7170,7 +7210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9330,6 +9370,46 @@
         <v>1003</v>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>428.7</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5338,6 +5338,46 @@
         <v>428.7</v>
       </c>
       <c r="H123" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>FYO035</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>765.1</v>
+      </c>
+      <c r="H124" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7210,7 +7250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9410,6 +9450,46 @@
         <v>428.7</v>
       </c>
       <c r="H55" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>FYO035</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>765.1</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5380,6 +5380,46 @@
       <c r="H124" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>FVO035</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1660</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Veolia había dicho que mandaría un carro con capacidad de 4 ton. Quedaron aproximadamente 1,5 ton en el acopio de willy. </t>
         </is>
       </c>
     </row>
@@ -5394,7 +5434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7276,46 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>May_2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FVO035</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1660</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Veolia había dicho que mandaría un carro con capacidad de 4 ton. Quedaron aproximadamente 1,5 ton en el acopio de willy. </t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5420,6 +5420,46 @@
       <c r="H125" t="inlineStr">
         <is>
           <t xml:space="preserve">Veolia había dicho que mandaría un carro con capacidad de 4 ton. Quedaron aproximadamente 1,5 ton en el acopio de willy. </t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9570,6 +9610,46 @@
         <v>765.1</v>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Hernan Alonso</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5458,6 +5458,46 @@
         <v>289.9</v>
       </c>
       <c r="H126" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="H127" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -5474,7 +5514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7356,6 +7396,46 @@
       <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve">Veolia había dicho que mandaría un carro con capacidad de 4 ton. Quedaron aproximadamente 1,5 ton en el acopio de willy. </t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SVD375</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5498,6 +5498,46 @@
         <v>317.2</v>
       </c>
       <c r="H127" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Cartón contaminado</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>210</v>
+      </c>
+      <c r="H128" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -10658,7 +10698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10823,6 +10863,46 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Recicla Oriente</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cartón contaminado</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>210</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5519,11 +5519,7 @@
           <t>Recicla Oriente</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>ABC123</t>
@@ -5540,6 +5536,46 @@
       <c r="H128" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>SVO395</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>564.8</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Solo se llevaron lo que había en el pasillo, los IBC estan a tope.</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9772,6 +9808,46 @@
       <c r="H57" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Oscar Javier</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SVO395</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>564.8</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Solo se llevaron lo que había en el pasillo, los IBC estan a tope.</t>
         </is>
       </c>
     </row>
@@ -10879,11 +10955,7 @@
           <t>Recicla Oriente</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>ABC123</t>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5576,6 +5576,222 @@
       <c r="H129" t="inlineStr">
         <is>
           <t>Solo se llevaron lo que había en el pasillo, los IBC estan a tope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>387.25</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>PET sucio</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10758,6 +10974,222 @@
         <v>94.09999999999999</v>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cartón limpio</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tubo plega</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>387.25</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PET sucio</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CORPOGESTAR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5792,6 +5792,46 @@
       <c r="H135" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Venian solo con esa capacidad disponible, adicional comentaron que iban a enviar un carro completo pero que hubo inconvenientes...</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7728,6 +7768,46 @@
       <c r="H48" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Venian solo con esa capacidad disponible, adicional comentaron que iban a enviar un carro completo pero que hubo inconvenientes...</t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5832,6 +5832,46 @@
       <c r="H136" t="inlineStr">
         <is>
           <t>Venian solo con esa capacidad disponible, adicional comentaron que iban a enviar un carro completo pero que hubo inconvenientes...</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>341.6</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10144,6 +10184,46 @@
       <c r="H58" t="inlineStr">
         <is>
           <t>Solo se llevaron lo que había en el pasillo, los IBC estan a tope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>341.6</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5870,6 +5870,46 @@
         <v>341.6</v>
       </c>
       <c r="H137" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="H138" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7862,7 +7902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10222,6 +10262,46 @@
         <v>341.6</v>
       </c>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Hernan Agudelo</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5910,6 +5910,46 @@
         <v>239.5</v>
       </c>
       <c r="H138" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Carlos Torres</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>LMC732</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>2889</v>
+      </c>
+      <c r="H139" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -5926,7 +5966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7888,6 +7928,46 @@
       <c r="H49" t="inlineStr">
         <is>
           <t>Venian solo con esa capacidad disponible, adicional comentaron que iban a enviar un carro completo pero que hubo inconvenientes...</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Carlos Torres</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LMC732</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>2889</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5950,6 +5950,46 @@
         <v>2889</v>
       </c>
       <c r="H139" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Carlos Torres</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>LMC732</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1500.6</v>
+      </c>
+      <c r="H140" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7982,7 +8022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10382,6 +10422,46 @@
         <v>239.5</v>
       </c>
       <c r="H60" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Carlos Torres</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LMC732</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1500.6</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5990,6 +5990,126 @@
         <v>1500.6</v>
       </c>
       <c r="H140" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>247.7</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Sólidos con químicos</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Torner</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H143" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -8022,7 +8142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10462,6 +10582,126 @@
         <v>1500.6</v>
       </c>
       <c r="H61" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>247.7</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Sólidos con químicos</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Torner</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6011,11 +6011,7 @@
           <t>VEOLIA Peligrosos</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>FVY530</t>
@@ -6051,11 +6047,7 @@
           <t>VEOLIA Peligrosos</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>FVY530</t>
@@ -6091,11 +6083,7 @@
           <t>VEOLIA Peligrosos</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>FVY530</t>
@@ -6112,6 +6100,86 @@
       <c r="H143" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venía un camión muy pequeño. Dijeron que el martes 30/06 vienen a recoger. Solo recogieron los plsticos contaminados de estampación, filtros y tubos de dqo. </t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Residuos laboratorio</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venía un camión muy pequeño. Dijeron que el martes 30/06 vienen a recoger. Solo recogieron los plsticos contaminados de estampación, filtros y tubos de dqo. </t>
         </is>
       </c>
     </row>
@@ -8142,7 +8210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10603,11 +10671,7 @@
           <t>VEOLIA Peligrosos</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>FVY530</t>
@@ -10643,11 +10707,7 @@
           <t>VEOLIA Peligrosos</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>FVY530</t>
@@ -10683,11 +10743,7 @@
           <t>VEOLIA Peligrosos</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>FVY530</t>
@@ -10704,6 +10760,86 @@
       <c r="H64" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venía un camión muy pequeño. Dijeron que el martes 30/06 vienen a recoger. Solo recogieron los plsticos contaminados de estampación, filtros y tubos de dqo. </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>June_2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Residuos laboratorio</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venía un camión muy pequeño. Dijeron que el martes 30/06 vienen a recoger. Solo recogieron los plsticos contaminados de estampación, filtros y tubos de dqo. </t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6180,6 +6180,46 @@
       <c r="H145" t="inlineStr">
         <is>
           <t xml:space="preserve">Venía un camión muy pequeño. Dijeron que el martes 30/06 vienen a recoger. Solo recogieron los plsticos contaminados de estampación, filtros y tubos de dqo. </t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10840,6 +10880,46 @@
       <c r="H66" t="inlineStr">
         <is>
           <t xml:space="preserve">Venía un camión muy pequeño. Dijeron que el martes 30/06 vienen a recoger. Solo recogieron los plsticos contaminados de estampación, filtros y tubos de dqo. </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6218,6 +6218,86 @@
         <v>1095</v>
       </c>
       <c r="H146" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>946.7</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aceite </t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>436.5</v>
+      </c>
+      <c r="H148" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -8250,7 +8330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10918,6 +10998,86 @@
         <v>1095</v>
       </c>
       <c r="H67" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>946.7</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aceite </t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>436.5</v>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6298,6 +6298,46 @@
         <v>436.5</v>
       </c>
       <c r="H148" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="H149" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6314,7 +6354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8314,6 +8354,46 @@
         <v>2889</v>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6338,6 +6338,126 @@
         <v>115.5</v>
       </c>
       <c r="H149" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>209.6</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Toner</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="H152" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -8410,7 +8530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11158,6 +11278,126 @@
         <v>436.5</v>
       </c>
       <c r="H69" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>209.6</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Toner</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jaime Gomez</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6460,6 +6460,46 @@
       <c r="H152" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>238.7</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se comprometieron a venir con la frecuencia establecida pero recogiendo aproximadamente solo 200 kg. </t>
         </is>
       </c>
     </row>
@@ -6474,7 +6514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8516,6 +8556,46 @@
       <c r="H51" t="inlineStr">
         <is>
           <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>238.7</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se comprometieron a venir con la frecuencia establecida pero recogiendo aproximadamente solo 200 kg. </t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6500,6 +6500,86 @@
       <c r="H153" t="inlineStr">
         <is>
           <t xml:space="preserve">Se comprometieron a venir con la frecuencia establecida pero recogiendo aproximadamente solo 200 kg. </t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>278</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>91</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11478,6 +11558,86 @@
         <v>56.3</v>
       </c>
       <c r="H72" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>278</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jaime Suarez</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>91</v>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6578,6 +6578,46 @@
         <v>91</v>
       </c>
       <c r="H155" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="H156" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6594,7 +6634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8676,6 +8716,46 @@
       <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve">Se comprometieron a venir con la frecuencia establecida pero recogiendo aproximadamente solo 200 kg. </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SVO375</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6618,6 +6618,46 @@
         <v>237.5</v>
       </c>
       <c r="H156" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -8770,7 +8810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11718,6 +11758,46 @@
         <v>91</v>
       </c>
       <c r="H74" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6658,6 +6658,46 @@
         <v>387.1</v>
       </c>
       <c r="H157" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="H158" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6674,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8794,6 +8834,46 @@
         <v>237.5</v>
       </c>
       <c r="H53" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6698,6 +6698,46 @@
         <v>235.5</v>
       </c>
       <c r="H158" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>22</v>
+      </c>
+      <c r="H159" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6714,7 +6754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8874,6 +8914,46 @@
         <v>235.5</v>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>22</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6738,6 +6738,46 @@
         <v>22</v>
       </c>
       <c r="H159" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>496.6</v>
+      </c>
+      <c r="H160" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -8970,7 +9010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11958,6 +11998,46 @@
         <v>387.1</v>
       </c>
       <c r="H75" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SUO375</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>496.6</v>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
